--- a/assets/docs/01_Client_Database.xlsx
+++ b/assets/docs/01_Client_Database.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Database" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Database'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Database'!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,6 +29,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,7 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="001F1A12"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +57,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,17 +430,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,154 +469,270 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Last Contact</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Next Follow-up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CL-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Maria Santos</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Santos Events</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>maria@example.com</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Design Support</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Avery Santos</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>BrightPath Creative Studio</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>avery@brightpath.example</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>555-0101</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Production Coordination</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Weekly production check-in</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CL-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Daniel Cruz</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DC Marketing</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>daniel@example.com</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Admin Support</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BP-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Mika Reyes</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BrightPath Creative Studio</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>mika@brightpath.example</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>555-0102</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Support</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Invoice follow-up</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CL-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Anna Reyes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AR Consulting</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>anna@example.com</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VA Support</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BP-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jordan Cruz</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>BrightPath Creative Studio</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>jordan@brightpath.example</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>555-0103</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Creative Project Support</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Awaiting onboarding documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sam Flores</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>BrightPath Creative Studio</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>sam@brightpath.example</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>555-0104</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>File Organization</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Drive structure confirmation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"New,Pending,Active,Completed,On Hold"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:K5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>